--- a/Stats Sheet/Round Gaps/Addiction.xlsx
+++ b/Stats Sheet/Round Gaps/Addiction.xlsx
@@ -538,10 +538,10 @@
     <x:t>5hup</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
-  </x:si>
-  <x:si>
     <x:t>MarcC5M</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>Odennn</x:t>
@@ -3973,18 +3973,9 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D113" s="0">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="S113" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="T113" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="U113" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="V113" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
@@ -3999,9 +3990,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D114" s="0">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="S114" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="T114" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="U114" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="V114" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
